--- a/AAII_Financials/Quarterly/PPCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPCB_QTR_FIN.xlsx
@@ -10728,7 +10728,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
